--- a/老余裸K圖表_20260616/老余裸K_賺賠比精選_20260616.xlsx
+++ b/老余裸K圖表_20260616/老余裸K_賺賠比精選_20260616.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -547,33 +547,33 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>7751.TWO</t>
+          <t>4577.TWO</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>達航科技</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>1 : 7.16</t>
+          <t>1 : 17.07</t>
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>1445</v>
+        <v>91</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>1255</v>
+        <v>85.2</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>2805</v>
+        <v>190</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>190</v>
+        <v>5.8</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>522</v>
+        <v>739</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -584,33 +584,33 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>3163.TWO</t>
+          <t>2630.TW</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>波若威</t>
+          <t>亞航</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>1 : 5.49</t>
+          <t>1 : 11.21</t>
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>876</v>
+        <v>39.35</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>796</v>
+        <v>38.15</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>1315</v>
+        <v>52.8</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>80</v>
+        <v>1.2</v>
       </c>
       <c r="H3" s="10" t="n">
-        <v>4635</v>
+        <v>860</v>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
@@ -621,33 +621,33 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>6199.TWO</t>
+          <t>3339.TWO</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>天品</t>
+          <t>泰谷</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>1 : 4.56</t>
+          <t>1 : 6.44</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>92.3</v>
+        <v>45</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>87.09999999999999</v>
+        <v>40.7</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>116</v>
+        <v>72.7</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>901</v>
+        <v>3590</v>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
@@ -658,33 +658,33 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>3466.TWO</t>
+          <t>3543.TW</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>德晉</t>
+          <t>州巧</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>1 : 3.66</t>
+          <t>1 : 5.65</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>33.55</v>
+        <v>32.55</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>45.8</v>
+        <v>46.4</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>3.35</v>
+        <v>2.45</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>1198</v>
+        <v>503</v>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
@@ -695,33 +695,33 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>4991.TWO</t>
+          <t>1569.TWO</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>環宇-KY</t>
+          <t>濱川</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>1 : 3.03</t>
+          <t>1 : 4.57</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>587</v>
+        <v>49.85</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>485.5</v>
+        <v>46.05</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>895</v>
+        <v>67.2</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>101.5</v>
+        <v>3.8</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>7307</v>
+        <v>938</v>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
@@ -732,33 +732,33 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>3339.TWO</t>
+          <t>6426.TW</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>泰谷</t>
+          <t>統新</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>1 : 2.64</t>
+          <t>1 : 4.36</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>49.5</v>
+        <v>209</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>40.7</v>
+        <v>189.5</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>72.7</v>
+        <v>294</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>8.800000000000001</v>
+        <v>19.5</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>6808</v>
+        <v>1274</v>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
@@ -769,33 +769,33 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>6919.TW</t>
+          <t>6909.TW</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>創控</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>1 : 2.33</t>
+          <t>1 : 4.21</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>96.59999999999999</v>
+        <v>47.65</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>87</v>
+        <v>42.3</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>119</v>
+        <v>70.16</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>9.6</v>
+        <v>5.35</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>3181</v>
+        <v>709</v>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
@@ -806,35 +806,368 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>6725.TWO</t>
+          <t>3062.TW</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>矽科宏晟</t>
+          <t>建漢</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>1 : 2.21</t>
+          <t>1 : 3.79</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>320</v>
+        <v>26</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>273</v>
+        <v>24.05</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>424</v>
+        <v>33.4</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>47</v>
+        <v>1.95</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>534</v>
+        <v>4371</v>
       </c>
       <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2419.TW</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>仲琦</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>1 : 3.65</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>27.35</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>2221</v>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>6683.TWO</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>雍智科技</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>1 : 3.38</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>1585</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>1295</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>2565</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>290</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>1401</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>3031.TW</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>佰鴻</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>1 : 3.27</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>700</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>3081.TWO</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>1 : 3.13</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>2335</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>3305</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>310</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>1960</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>6584.TWO</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>南俊國際</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>1 : 2.84</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>625</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>544</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>855</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>556</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>3689.TWO</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>湧德</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>1 : 2.79</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>110</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>146</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>1905</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>6919.TW</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>康霈*</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>1 : 2.76</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>119</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>4260</v>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>3289.TWO</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>宜特</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>1 : 2.5</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>169</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>149</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>219</v>
+      </c>
+      <c r="G17" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>1902</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>1301.TW</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>台塑</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>1 : 2.18</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>47.25</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>36007</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>點我查看</t>
         </is>
@@ -850,6 +1183,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
